--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121101445</v>
+        <v>121101416</v>
       </c>
       <c r="B2" t="n">
-        <v>56552</v>
+        <v>56555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567105</v>
+        <v>567072</v>
       </c>
       <c r="R2" t="n">
-        <v>6415959</v>
+        <v>6415968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -771,7 +771,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Samma ex</t>
+          <t>Sedd och hörd i avverkningsanmälan. Äldre tallskog med rikligt uppslag av yngre gran. Höll till i tätare och lite fuktigt parti.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101416</v>
+        <v>121101445</v>
       </c>
       <c r="B3" t="n">
-        <v>56552</v>
+        <v>56555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567072</v>
+        <v>567105</v>
       </c>
       <c r="R3" t="n">
-        <v>6415968</v>
+        <v>6415959</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sedd och hörd i avverkningsanmälan. Äldre tallskog med rikligt uppslag av yngre gran. Höll till i tätare och lite fuktigt parti.</t>
+          <t>Samma ex</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121101416</v>
+        <v>121101445</v>
       </c>
       <c r="B2" t="n">
         <v>56555</v>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567072</v>
+        <v>567105</v>
       </c>
       <c r="R2" t="n">
-        <v>6415968</v>
+        <v>6415959</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -771,7 +771,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sedd och hörd i avverkningsanmälan. Äldre tallskog med rikligt uppslag av yngre gran. Höll till i tätare och lite fuktigt parti.</t>
+          <t>Samma ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101445</v>
+        <v>121101416</v>
       </c>
       <c r="B3" t="n">
         <v>56555</v>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567105</v>
+        <v>567072</v>
       </c>
       <c r="R3" t="n">
-        <v>6415959</v>
+        <v>6415968</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Samma ex</t>
+          <t>Sedd och hörd i avverkningsanmälan. Äldre tallskog med rikligt uppslag av yngre gran. Höll till i tätare och lite fuktigt parti.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121101445</v>
+        <v>121101416</v>
       </c>
       <c r="B2" t="n">
-        <v>56555</v>
+        <v>56558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567105</v>
+        <v>567072</v>
       </c>
       <c r="R2" t="n">
-        <v>6415959</v>
+        <v>6415968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -771,7 +771,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Samma ex</t>
+          <t>Sedd och hörd i avverkningsanmälan. Äldre tallskog med rikligt uppslag av yngre gran. Höll till i tätare och lite fuktigt parti.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101416</v>
+        <v>121101445</v>
       </c>
       <c r="B3" t="n">
-        <v>56555</v>
+        <v>56558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567072</v>
+        <v>567105</v>
       </c>
       <c r="R3" t="n">
-        <v>6415968</v>
+        <v>6415959</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sedd och hörd i avverkningsanmälan. Äldre tallskog med rikligt uppslag av yngre gran. Höll till i tätare och lite fuktigt parti.</t>
+          <t>Samma ex</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>121101416</v>
       </c>
       <c r="B2" t="n">
-        <v>56558</v>
+        <v>56680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121101416</v>
       </c>
       <c r="B2" t="n">
-        <v>56680</v>
+        <v>56683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121101416</v>
       </c>
       <c r="B2" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45462-2024 artfynd.xlsx
+++ b/artfynd/A 45462-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121101416</v>
       </c>
       <c r="B2" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
